--- a/data/export/2026-09-18-operations.xlsx
+++ b/data/export/2026-09-18-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -648,24 +648,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>67分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站德川路华夏东路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -719,22 +719,22 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站博兴路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -896,29 +896,29 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>06:21采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
@@ -1025,19 +1025,19 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 34分钟</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,33 +1072,37 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1140,31 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1164,7 +1172,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1188,17 +1196,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1208,13 +1216,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1257,24 +1269,24 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1284,7 +1296,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1313,7 +1325,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1333,12 +1345,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1381,19 +1393,19 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数77分钟估算，约±6分钟</t>
+          <t>07:21采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1408,7 +1420,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1437,7 +1449,7 @@
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1457,12 +1469,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>6/13</t>
         </is>
       </c>
     </row>
@@ -1475,24 +1487,24 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -1505,34 +1517,34 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±5分钟</t>
+          <t>07:21采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±14分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1546,7 +1558,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1556,12 +1568,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1581,40 +1593,40 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>6/8</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1629,34 +1641,34 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站博兴路兰城路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±9分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1670,7 +1682,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1685,7 +1697,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1705,40 +1717,40 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>9/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1753,19 +1765,19 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+          <t>07:21采样：该车到重点站东陆路金海路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1775,12 +1787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1794,7 +1806,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1829,40 +1841,40 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1877,34 +1889,34 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±9分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1930,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1953,40 +1965,40 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>10/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2001,30 +2013,34 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2054,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -2048,61 +2064,65 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2117,30 +2137,34 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2178,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2164,17 +2188,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2184,41 +2208,45 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>12/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2233,30 +2261,34 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2302,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2280,17 +2312,17 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2300,41 +2332,45 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>13/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2349,34 +2385,34 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数152分钟估算，约±7分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2390,7 +2426,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2415,50 +2451,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>8/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A31963D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2473,19 +2509,19 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数164分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2495,12 +2531,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2514,7 +2550,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2539,40 +2575,40 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/8</t>
+          <t>7/13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2582,7 +2618,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2597,30 +2633,34 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：06:20采样，终点ETA 85分钟</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>07:20采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2644,17 +2684,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2664,41 +2704,45 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2713,34 +2757,34 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数92分钟估算，约±14分钟</t>
+          <t>07:20采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2754,7 +2798,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2764,12 +2808,12 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2789,40 +2833,40 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2837,34 +2881,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数113分钟估算，约±15分钟</t>
+          <t>06:50采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2878,7 +2922,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2888,12 +2932,12 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2913,40 +2957,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>2/4</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2979,12 +3023,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2998,7 +3042,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3034,7 +3078,3903 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>164分钟</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>164.0</t>
+        </is>
+      </c>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>07:12采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>8/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>8/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>159分钟</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数159分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数151分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>171分钟</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数171分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>13/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：07:12采样，终点ETA 50分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>10/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>4/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>106分钟</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>13/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>08:17</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>3/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>100分钟</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>11/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>07:12采样：该车到重点站张杨北路五莲路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>8/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>8/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站张杨北路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>5/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>2/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>12/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>79分钟</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>1/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>09:28</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>6/16</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/16</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-operations.xlsx
+++ b/data/export/2026-09-18-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -452,7 +452,7 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,22 +843,22 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1037,10 +1037,14 @@
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:21采样，终点ETA 34分钟</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,12 +1076,12 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1102,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1145,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1172,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1211,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1264,29 +1268,29 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站唐陆公路锦绣东路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数31分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1296,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1320,12 +1324,12 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1335,22 +1339,22 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1388,29 +1392,29 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站东陆路金海路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1420,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1444,12 +1448,12 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
@@ -1459,22 +1463,22 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>6/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1512,29 +1516,29 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:27</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站新德西路德翔路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1544,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1568,12 +1572,12 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1583,22 +1587,22 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1641,24 +1645,24 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±8分钟</t>
+          <t>08:11采样：该车到重点站金杨路金业路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数9分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1668,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1697,7 +1701,7 @@
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1717,12 +1721,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>9/13</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1765,26 +1769,22 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>07:21采样：该车到重点站东陆路金海路 ETA 20分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:11采样，终点ETA 27分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1816,12 +1816,12 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1889,24 +1889,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数87分钟估算，约±6分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>10/13</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2013,24 +2013,24 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±6分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路顾家浜路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2137,19 +2137,19 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+          <t>08:01采样：该车到重点站唐陆公路唐镇路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>12/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2266,19 +2266,19 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±12分钟</t>
+          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2312,12 +2312,12 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>13/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2385,24 +2385,24 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±5分钟</t>
+          <t>08:11采样：该车到重点站荷泽路长岛路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2441,7 +2441,7 @@
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>8/13</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2479,24 +2479,24 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31963D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -2509,24 +2509,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2550,7 +2550,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2585,40 +2585,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>7/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A31963D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2633,34 +2633,34 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±7分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2674,7 +2674,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2699,50 +2699,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2757,34 +2757,34 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2823,50 +2823,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2881,34 +2881,34 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>06:50采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数95分钟估算，约±10分钟</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2922,7 +2922,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2957,40 +2957,40 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3005,30 +3005,34 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3042,7 +3046,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -3052,61 +3056,65 @@
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3121,30 +3129,34 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3158,7 +3170,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3168,61 +3180,65 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3255,12 +3271,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3274,7 +3290,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3299,18 +3315,22 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3323,24 +3343,24 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3348,29 +3368,29 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3380,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3394,7 +3414,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3404,12 +3424,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3429,12 +3449,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3467,7 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3457,7 +3477,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3472,39 +3492,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>07:12采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3518,7 +3538,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3528,12 +3548,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3543,22 +3563,22 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3591,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3581,7 +3601,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3601,34 +3621,34 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+          <t>06:50采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3642,7 +3662,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3677,12 +3697,12 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3715,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3705,7 +3725,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3725,34 +3745,30 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3766,7 +3782,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3776,17 +3792,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3796,17 +3812,13 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3819,7 +3831,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3829,7 +3841,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3849,34 +3861,30 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3890,7 +3898,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3900,17 +3908,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3920,17 +3928,13 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr">
-        <is>
-          <t>160.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3943,24 +3947,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3973,30 +3977,30 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>172分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 82分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4010,7 +4014,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4025,7 +4029,7 @@
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -4046,7 +4050,7 @@
       <c r="AC29" s="2" t="inlineStr"/>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4063,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -4069,7 +4073,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -4089,34 +4093,34 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±9分钟</t>
+          <t>08:10采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4130,7 +4134,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4145,7 +4149,7 @@
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4165,12 +4169,12 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4187,7 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -4193,7 +4197,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4213,30 +4217,34 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>182分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>08:10采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4250,7 +4258,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4260,17 +4268,17 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4280,13 +4288,17 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>182.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4311,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4309,7 +4321,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4329,34 +4341,34 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数159分钟估算，约±8分钟</t>
+          <t>08:10采样：该车到重点站浦建路锦绣路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4370,7 +4382,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4385,7 +4397,7 @@
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4405,12 +4417,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4435,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4433,7 +4445,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4453,30 +4465,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>08:10采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4490,7 +4506,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4500,17 +4516,17 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4520,13 +4536,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4559,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4549,7 +4569,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4569,19 +4589,19 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数151分钟估算，约±6分钟</t>
+          <t>08:10采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4591,12 +4611,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4610,7 +4630,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4625,7 +4645,7 @@
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4645,12 +4665,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4683,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4673,7 +4693,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4693,34 +4713,30 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数171分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4734,7 +4750,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4744,17 +4760,17 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4764,17 +4780,13 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr">
-        <is>
-          <t>171.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4787,24 +4799,24 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4817,34 +4829,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
           <t>07:12</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4858,7 +4870,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4893,40 +4905,40 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>4/19</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4941,30 +4953,30 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:12采样，终点ETA 50分钟</t>
+          <t>尚无满足±5分钟标准的终点ETA</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4978,7 +4990,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4993,7 +5005,7 @@
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -5003,7 +5015,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -5014,35 +5026,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -5057,34 +5069,34 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数33分钟，约±12分钟</t>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5098,7 +5110,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5108,7 +5120,7 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
@@ -5133,40 +5145,40 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>10/16</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5181,34 +5193,30 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数45分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5222,7 +5230,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5232,17 +5240,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5252,45 +5260,41 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>4/16</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5305,34 +5309,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站巨峰路成园路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±8分钟</t>
+          <t>08:10采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5346,7 +5350,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5381,40 +5385,40 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>13/16</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5429,34 +5433,34 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>176分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站五莲路荷泽路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数154分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5470,7 +5474,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5505,40 +5509,40 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>3/16</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5553,30 +5557,34 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>08:10采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5590,7 +5598,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5600,17 +5608,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5620,41 +5628,45 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5669,34 +5681,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数75分钟，约±15分钟</t>
+          <t>08:01采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数170分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5710,7 +5722,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5720,7 +5732,7 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
@@ -5745,40 +5757,40 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>11/16</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5793,19 +5805,19 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>07:12采样：该车到重点站张杨北路五莲路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站浦东大道东波路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5815,12 +5827,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5834,7 +5846,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5869,40 +5881,40 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5917,34 +5929,30 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站杨高北路夏碧路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±11分钟</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5958,7 +5966,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5968,17 +5976,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5988,45 +5996,41 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>8/16</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -6041,22 +6045,26 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N46" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -6064,7 +6072,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6078,7 +6086,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6088,17 +6096,17 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6108,41 +6116,45 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/16</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6157,34 +6169,30 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>08:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr"/>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站张杨北路大同路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6198,7 +6206,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6208,17 +6216,17 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6228,45 +6236,41 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC47" s="2" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>5/16</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6281,34 +6285,30 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6322,7 +6322,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6332,17 +6332,17 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6352,45 +6352,41 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>2/16</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6405,34 +6401,30 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数104分钟估算，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6446,7 +6438,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6456,17 +6448,17 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6476,45 +6468,41 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>12/16</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6529,34 +6517,34 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±11分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6570,7 +6558,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6580,7 +6568,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6605,40 +6593,40 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6653,34 +6641,34 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数79分钟估算，约±10分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6694,7 +6682,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6719,22 +6707,22 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>1/16</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -6747,7 +6735,7 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -6757,7 +6745,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6777,26 +6765,22 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数94分钟估算，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：07:50采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6804,7 +6788,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6818,7 +6802,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6833,7 +6817,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6843,22 +6827,22 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>6/16</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6871,24 +6855,24 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6901,19 +6885,19 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr"/>
@@ -6924,7 +6908,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6938,43 +6922,2763 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>08:12</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>92分钟</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>110分钟</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 29分钟</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>末次终点ETA兜底</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>105分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>07:50采样：该车到重点站五莲路凌河路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数23分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>同车反向发车反推</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>102分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站杨高北路洲海路（外高桥保税区） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±11分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>101分钟</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金高路源华路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>09:13</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>103分钟</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站五莲路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>98分钟</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站航津路地铁站 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="W53" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>93分钟</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站金杨路金桥路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±13分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X53" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>100.5</t>
+        </is>
+      </c>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>112分钟</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数112分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:19</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr"/>
-      <c r="AD53" s="2" t="inlineStr">
-        <is>
-          <t>—/16</t>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-operations.xlsx
+++ b/data/export/2026-09-18-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD75"/>
+  <dimension ref="A1:AD78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1645,26 +1645,22 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站金杨路金业路 ETA 26分钟；叠加该车自身同类时段从该站到终点历史中位数9分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:21采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1672,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1696,12 +1692,12 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1711,22 +1707,22 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1831,22 +1827,22 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1889,24 +1885,24 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路台桥路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±8分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1916,7 +1912,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1965,12 +1961,12 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2013,19 +2009,19 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路顾家浜路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -2040,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2089,7 +2085,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2137,19 +2133,19 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站唐陆公路唐镇路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±5分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2164,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2213,12 +2209,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2261,24 +2257,24 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站唐陆公路唐龙路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±6分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路龙东大道 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -2288,7 +2284,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2337,12 +2333,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2385,24 +2381,24 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>08:11采样：该车到重点站荷泽路长岛路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数76分钟，约±7分钟</t>
+          <t>08:21采样：该车到重点站唐陆公路川桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2412,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2461,12 +2457,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2509,19 +2505,19 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数100分钟估算，约±9分钟</t>
+          <t>08:21采样：该车到重点站德川路华夏东路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2536,7 +2532,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2565,7 +2561,7 @@
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2585,7 +2581,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
@@ -2660,7 +2656,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2714,7 +2710,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2757,24 +2753,24 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±8分钟</t>
+          <t>08:21采样：该车到重点站新川路华东路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2784,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2813,7 +2809,7 @@
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2833,12 +2829,12 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2904,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2962,7 +2958,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3156,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3210,7 +3206,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3325,40 +3321,40 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3368,39 +3364,39 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数89分钟估算，约±10分钟</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3414,7 +3410,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3424,12 +3420,12 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3439,50 +3435,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3492,39 +3488,39 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数88分钟估算，约±12分钟</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3538,7 +3534,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3548,12 +3544,12 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3573,12 +3569,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3587,7 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3601,7 +3597,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3616,29 +3612,29 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>06:50采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3648,7 +3644,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3662,7 +3658,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3672,12 +3668,12 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3687,22 +3683,22 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3711,7 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3725,7 +3721,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3740,27 +3736,31 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3792,33 +3792,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3831,7 +3835,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3841,7 +3845,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3861,22 +3865,26 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>06:50采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3884,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3898,7 +3906,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3908,17 +3916,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3928,13 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3947,24 +3959,24 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>06:41</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3977,30 +3989,30 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 82分钟</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 48分钟</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4014,7 +4026,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4063,24 +4075,24 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4093,26 +4105,22 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4120,7 +4128,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4134,7 +4142,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4144,17 +4152,17 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4164,17 +4172,13 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>159.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -4187,24 +4191,24 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4212,29 +4216,29 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>182分钟</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
@@ -4244,7 +4248,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4258,7 +4262,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4268,12 +4272,12 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4293,12 +4297,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>171.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4311,24 +4315,24 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:55</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4341,34 +4345,34 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站浦建路锦绣路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±9分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4382,7 +4386,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4417,7 +4421,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
@@ -4435,7 +4439,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4445,7 +4449,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4465,34 +4469,34 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>179分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±10分钟</t>
+          <t>08:20采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4506,7 +4510,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4541,12 +4545,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>179.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4563,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4569,7 +4573,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4589,34 +4593,34 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±6分钟</t>
+          <t>08:20采样：该车到重点站浦建路锦绣路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4630,7 +4634,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:55</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4665,12 +4669,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4687,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4693,7 +4697,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4713,30 +4717,34 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站沪南路高科西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4750,7 +4758,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4760,17 +4768,17 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4780,13 +4788,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>175.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -4799,24 +4811,24 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4829,34 +4841,34 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±9分钟</t>
+          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4870,7 +4882,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4885,7 +4897,7 @@
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4905,12 +4917,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4935,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4933,7 +4945,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4976,7 +4988,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4990,7 +5002,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -5039,24 +5051,24 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:25</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5074,14 +5086,14 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±9分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -5096,7 +5108,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5110,7 +5122,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5125,7 +5137,7 @@
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -5145,12 +5157,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5175,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A52272D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5173,7 +5185,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5211,12 +5223,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5230,7 +5242,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5279,7 +5291,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5289,7 +5301,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5309,34 +5321,34 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站白桦路明月路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5350,7 +5362,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5385,12 +5397,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -5403,7 +5415,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A52272D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5413,7 +5425,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5433,34 +5445,30 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>176分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数154分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5474,7 +5482,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5484,17 +5492,17 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5504,17 +5512,13 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>176.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5531,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5537,7 +5541,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5557,7 +5561,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5569,22 +5573,22 @@
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
+          <t>08:20采样：该车到重点站白桦路明月路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5598,7 +5602,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5651,7 +5655,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5661,7 +5665,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5681,34 +5685,34 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>181分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数170分钟，约±9分钟</t>
+          <t>08:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5722,7 +5726,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5757,12 +5761,12 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -5775,7 +5779,7 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -5785,7 +5789,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -5805,34 +5809,34 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站浦东大道东波路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5846,7 +5850,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5881,12 +5885,12 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -5899,7 +5903,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5909,7 +5913,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5929,25 +5933,29 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>181分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>08:01采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数170分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5966,7 +5974,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5976,17 +5984,17 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5996,13 +6004,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -6015,24 +6027,24 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:18</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6045,19 +6057,19 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±5分钟</t>
+          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -6067,12 +6079,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6086,7 +6098,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6101,7 +6113,7 @@
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -6121,12 +6133,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -6139,22 +6151,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:20</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6192,7 +6204,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6206,7 +6218,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6255,7 +6267,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6265,7 +6277,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6285,30 +6297,34 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站康丽路康恩路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数162分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6322,7 +6338,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6332,17 +6348,17 @@
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6352,13 +6368,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>167.0</t>
+        </is>
+      </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6391,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6381,7 +6401,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6401,22 +6421,26 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr"/>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N49" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6424,7 +6448,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6438,7 +6462,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6448,17 +6472,17 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6468,13 +6492,17 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC49" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -6487,7 +6515,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6497,7 +6525,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6517,34 +6545,30 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6558,7 +6582,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6568,17 +6592,17 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6588,17 +6612,13 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>145.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6631,7 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -6621,7 +6641,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6641,26 +6661,22 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6668,7 +6684,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6682,7 +6698,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6692,65 +6708,61 @@
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>证据不足</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC51" s="2" t="inlineStr">
-        <is>
-          <t>149.5</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6765,30 +6777,34 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：07:50采样，终点ETA 7分钟</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6802,7 +6818,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6817,7 +6833,7 @@
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6827,50 +6843,50 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6885,30 +6901,34 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>08:17</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6922,7 +6942,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6937,7 +6957,7 @@
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6957,40 +6977,40 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -7000,39 +7020,39 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7046,7 +7066,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7056,12 +7076,12 @@
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -7081,12 +7101,12 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7119,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -7109,7 +7129,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7129,19 +7149,19 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>07:57</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>110分钟</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 29分钟</t>
+          <t>SHMAAS末次终点ETA推算：07:50采样，终点ETA 7分钟</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr"/>
@@ -7152,7 +7172,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7166,7 +7186,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7176,7 +7196,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7201,12 +7221,12 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7219,24 +7239,24 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7244,34 +7264,30 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:17</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7290,7 +7306,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7300,12 +7316,12 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7320,17 +7336,17 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7343,24 +7359,24 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7368,34 +7384,34 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>105分钟</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7414,7 +7430,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7424,12 +7440,12 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7439,22 +7455,22 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7467,7 +7483,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7477,7 +7493,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7497,34 +7513,30 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>07:50采样：该车到重点站五莲路凌河路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:00采样，终点ETA 29分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7538,7 +7550,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7548,12 +7560,12 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7563,12 +7575,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7578,7 +7590,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7603,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7601,7 +7613,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7616,29 +7628,29 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:27</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车08:45，减去该车自身同类时段历史终点停站中位数23分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
@@ -7648,7 +7660,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7662,7 +7674,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7672,12 +7684,12 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7697,12 +7709,12 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7715,7 +7727,7 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -7725,7 +7737,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7745,34 +7757,34 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>102分钟</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±8分钟</t>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7786,7 +7798,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7821,12 +7833,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7839,24 +7851,24 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7869,34 +7881,34 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>97分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站杨高北路洲海路（外高桥保税区） ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±11分钟</t>
+          <t>07:50采样：该车到重点站五莲路凌河路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7910,7 +7922,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7920,7 +7932,7 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7945,12 +7957,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7963,24 +7975,24 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>07:20</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -7993,34 +8005,30 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>101分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站巨峰路五莲路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8034,7 +8042,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -8044,12 +8052,12 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -8059,22 +8067,22 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8087,24 +8095,24 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8117,34 +8125,34 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金高路源华路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±6分钟</t>
+          <t>08:00采样：该车到重点站五莲路荷泽路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8158,7 +8166,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8193,12 +8201,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8211,24 +8219,24 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8241,19 +8249,19 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>103分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金高路俱进路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站花山路杨高北路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8263,12 +8271,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8282,7 +8290,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8317,12 +8325,12 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8343,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8345,7 +8353,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8365,34 +8373,34 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>08:00采样：该车到重点站金高路俱进路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站张杨北路博兴路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±15分钟</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8406,7 +8414,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8416,7 +8424,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8441,12 +8449,12 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8459,7 +8467,7 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -8469,7 +8477,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -8489,34 +8497,34 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站五莲路东陆路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站杨高北路（外高桥保税区南站） ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数27分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8530,7 +8538,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8565,12 +8573,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8583,7 +8591,7 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -8593,7 +8601,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8613,24 +8621,24 @@
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站航津路地铁站 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±8分钟</t>
+          <t>08:00采样：该车到重点站金高路俱进路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
@@ -8640,7 +8648,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8654,7 +8662,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8689,12 +8697,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8707,24 +8715,24 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A57902D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8737,34 +8745,34 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>93分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路金桥路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±13分钟</t>
+          <t>08:20采样：该车到重点站五莲路归昌路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8778,7 +8786,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8788,7 +8796,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8803,22 +8811,22 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>100.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8831,24 +8839,24 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -8861,34 +8869,34 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±8分钟</t>
+          <t>08:20采样：该车到重点站金高路行泰路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8902,7 +8910,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8917,7 +8925,7 @@
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8937,12 +8945,12 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8963,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8965,7 +8973,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8985,34 +8993,34 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数112分钟估算，约±6分钟</t>
+          <t>08:20采样：该车到重点站杨高北路航津路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9026,7 +9034,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -9041,7 +9049,7 @@
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -9051,22 +9059,22 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9087,7 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -9089,7 +9097,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -9109,24 +9117,24 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
+          <t>08:10采样：该车到重点站金杨路金桥路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±13分钟</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
@@ -9136,7 +9144,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9150,22 +9158,22 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>终点确认到达+2分钟（覆盖计划时间）</t>
+          <t>计划发车</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
@@ -9185,12 +9193,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>100.5</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9203,24 +9211,24 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9233,34 +9241,34 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数91分钟估算，约±8分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9274,7 +9282,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9284,7 +9292,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9309,12 +9317,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9327,7 +9335,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9337,7 +9345,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9357,22 +9365,26 @@
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数112分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9394,7 +9406,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9404,17 +9416,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车历史全程时间</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9424,17 +9436,17 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9447,7 +9459,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9457,7 +9469,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9477,19 +9489,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±9分钟</t>
+          <t>按该车自身同方向、同类时段历史全程时间中位数82分钟估算，约±9分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9518,12 +9530,12 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>计划发车</t>
+          <t>终点确认到达+2分钟（覆盖计划时间）</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
@@ -9553,12 +9565,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9571,24 +9583,24 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9601,30 +9613,34 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>按该车自身同方向、同类时段历史全程时间中位数86分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9638,47 +9654,411 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数80分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>08:45</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
+      <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AD75" s="2" t="inlineStr">
-        <is>
-          <t>1/18</t>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-operations.xlsx
+++ b/data/export/2026-09-18-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD162"/>
+  <dimension ref="A1:AD163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1096,17 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2708,17 +2708,17 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4440,17 +4440,17 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5476,27 +5476,31 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 36分钟</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5504,7 +5508,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5528,12 +5532,12 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5553,7 +5557,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5596,27 +5600,31 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 45分钟</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5624,7 +5632,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5648,12 +5656,12 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5673,12 +5681,12 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5721,19 +5729,19 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：12:31采样，终点ETA 45分钟</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr"/>
@@ -5744,7 +5752,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5768,17 +5776,17 @@
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5788,17 +5796,17 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5841,19 +5849,19 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr"/>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站唐陆公路龙东大道 ETA 32分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>12:31采样：该车到重点站东陆路新金桥路 ETA 33分钟；叠加该车自身同类时段从该站到终点历史中位数24分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5868,7 +5876,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5917,7 +5925,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="AD44" s="2" t="inlineStr">
@@ -5965,7 +5973,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5977,7 +5985,7 @@
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金桥路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>12:31采样：该车到重点站博兴路凌河路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5992,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6116,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6170,7 +6178,7 @@
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6248,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6364,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6488,7 +6496,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6542,7 +6550,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6608,7 +6616,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6657,12 +6665,12 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6740,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -7104,7 +7112,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -7153,7 +7161,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AD54" s="2" t="inlineStr">
@@ -7228,7 +7236,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7277,12 +7285,12 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7654,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7724,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7770,7 +7778,7 @@
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7848,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7889,12 +7897,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -8088,7 +8096,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8208,7 +8216,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8600,7 +8608,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8649,12 +8657,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8724,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8773,12 +8781,12 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8856,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8897,12 +8905,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8980,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9021,7 +9029,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
@@ -9096,7 +9104,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9145,7 +9153,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
@@ -9220,7 +9228,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9274,7 +9282,7 @@
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9352,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9393,12 +9401,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9600,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9641,12 +9649,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9778,7 @@
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9894,7 +9902,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10013,12 +10021,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10092,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10448,7 +10456,7 @@
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10497,12 +10505,12 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10580,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10621,7 +10629,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
@@ -10998,7 +11006,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11200,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11246,7 +11254,7 @@
       </c>
       <c r="AD87" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11324,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11365,12 +11373,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -11564,7 +11572,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11785,24 +11793,24 @@
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -11812,7 +11820,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11861,12 +11869,12 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11909,12 +11917,12 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
@@ -11936,7 +11944,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11985,12 +11993,12 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12028,27 +12036,31 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -12056,7 +12068,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12080,12 +12092,12 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -12105,7 +12117,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12148,27 +12160,31 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -12176,7 +12192,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12200,12 +12216,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -12225,12 +12241,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12273,19 +12289,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>12:31采样：该车到重点站长岛路张杨北路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -12300,7 +12316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12349,7 +12365,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12409,12 +12425,12 @@
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
+          <t>12:31采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
@@ -12424,7 +12440,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12478,7 +12494,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -12521,19 +12537,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路北中路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±7分钟</t>
+          <t>12:31采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12548,7 +12564,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12597,12 +12613,12 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -12645,24 +12661,24 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±9分钟</t>
+          <t>12:31采样：该车到重点站锦绣路罗山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
@@ -12672,7 +12688,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12721,12 +12737,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -12781,7 +12797,7 @@
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站丁香路锦绣路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±12分钟</t>
+          <t>12:31采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12796,7 +12812,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12893,19 +12909,19 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>12:31采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12920,7 +12936,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12969,12 +12985,12 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -13017,19 +13033,19 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±8分钟</t>
+          <t>12:31采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -13044,7 +13060,7 @@
       </c>
       <c r="P102" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q102" s="2" t="inlineStr">
@@ -13093,7 +13109,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AD102" s="2" t="inlineStr">
@@ -13141,19 +13157,19 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路高科西路 ETA 49分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±14分钟</t>
+          <t>12:31采样：该车到重点站沪南路高科西路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±14分钟</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -13168,7 +13184,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13217,12 +13233,12 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -13265,24 +13281,24 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±7分钟</t>
+          <t>12:31采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
@@ -13292,7 +13308,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13316,12 +13332,12 @@
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -13341,12 +13357,12 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13428,7 @@
       </c>
       <c r="P105" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q105" s="2" t="inlineStr">
@@ -13532,7 +13548,7 @@
       </c>
       <c r="P106" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q106" s="2" t="inlineStr">
@@ -13586,7 +13602,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -13656,7 +13672,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13780,7 +13796,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13900,7 +13916,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13949,12 +13965,12 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -14140,7 +14156,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14179,7 +14195,7 @@
       </c>
       <c r="AA111" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB111" s="2" t="inlineStr">
@@ -14264,7 +14280,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14313,12 +14329,12 @@
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -14384,7 +14400,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14433,7 +14449,7 @@
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
@@ -14562,7 +14578,7 @@
       </c>
       <c r="AD114" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -14752,7 +14768,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14806,7 +14822,7 @@
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -14876,7 +14892,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14925,7 +14941,7 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
@@ -15174,7 +15190,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -15244,7 +15260,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15293,12 +15309,12 @@
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -15368,7 +15384,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15488,7 +15504,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15537,7 +15553,7 @@
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
@@ -15736,7 +15752,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15785,7 +15801,7 @@
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
@@ -16232,7 +16248,7 @@
       </c>
       <c r="P128" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q128" s="2" t="inlineStr">
@@ -16281,12 +16297,12 @@
       </c>
       <c r="AC128" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -16356,7 +16372,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16395,7 +16411,7 @@
       </c>
       <c r="AA129" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB129" s="2" t="inlineStr">
@@ -16658,7 +16674,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -16724,7 +16740,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16773,7 +16789,7 @@
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
@@ -16848,7 +16864,7 @@
       </c>
       <c r="P133" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q133" s="2" t="inlineStr">
@@ -16897,7 +16913,7 @@
       </c>
       <c r="AC133" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD133" s="2" t="inlineStr">
@@ -17096,7 +17112,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17150,7 +17166,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -17274,7 +17290,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17484,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17592,7 +17608,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17641,12 +17657,12 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -17716,7 +17732,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17765,7 +17781,7 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
@@ -17840,7 +17856,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17889,7 +17905,7 @@
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
@@ -18088,7 +18104,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18127,7 +18143,7 @@
       </c>
       <c r="AA143" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB143" s="2" t="inlineStr">
@@ -18212,7 +18228,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18261,12 +18277,12 @@
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -18390,7 +18406,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -18460,7 +18476,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18509,7 +18525,7 @@
       </c>
       <c r="AC146" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AD146" s="2" t="inlineStr">
@@ -18584,7 +18600,7 @@
       </c>
       <c r="P147" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q147" s="2" t="inlineStr">
@@ -18633,7 +18649,7 @@
       </c>
       <c r="AC147" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD147" s="2" t="inlineStr">
@@ -18762,7 +18778,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -18832,7 +18848,7 @@
       </c>
       <c r="P149" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q149" s="2" t="inlineStr">
@@ -18886,7 +18902,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -18956,7 +18972,7 @@
       </c>
       <c r="P150" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q150" s="2" t="inlineStr">
@@ -19053,24 +19069,24 @@
       </c>
       <c r="I151" s="2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr"/>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N151" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O151" s="2" t="inlineStr">
@@ -19080,7 +19096,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19129,12 +19145,12 @@
       </c>
       <c r="AC151" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD151" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -19177,24 +19193,24 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
@@ -19204,7 +19220,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19253,7 +19269,7 @@
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
@@ -19301,12 +19317,12 @@
       </c>
       <c r="I153" s="2" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr"/>
@@ -19328,7 +19344,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19377,7 +19393,7 @@
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
@@ -19425,7 +19441,7 @@
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
@@ -19437,14 +19453,10 @@
       <c r="L154" s="2" t="inlineStr"/>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站五莲路凌河路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N154" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:30采样，终点ETA 44分钟</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr"/>
       <c r="O154" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -19452,7 +19464,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19476,12 +19488,12 @@
       </c>
       <c r="X154" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y154" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z154" s="2" t="inlineStr">
@@ -19491,7 +19503,7 @@
       </c>
       <c r="AA154" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB154" s="2" t="inlineStr">
@@ -19549,24 +19561,24 @@
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr"/>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站杨高北路航津路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±11分钟</t>
+          <t>12:30采样：该车到重点站金高路行泰路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±12分钟</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
@@ -19576,7 +19588,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19625,12 +19637,12 @@
       </c>
       <c r="AC155" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -19673,24 +19685,24 @@
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr"/>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>12:20采样：该车到重点站张杨北路金桥路 ETA 18分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±6分钟</t>
+          <t>12:30采样：该车到重点站张杨北路博兴路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
@@ -19700,7 +19712,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19749,7 +19761,7 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>92.2</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
@@ -19797,24 +19809,24 @@
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr"/>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数85分钟估算，约±8分钟</t>
+          <t>12:30采样：该车到重点站花山路杨高北路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
@@ -19824,7 +19836,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19853,7 +19865,7 @@
       </c>
       <c r="Y157" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z157" s="2" t="inlineStr">
@@ -19873,7 +19885,7 @@
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -19948,7 +19960,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20002,7 +20014,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -20068,7 +20080,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20192,7 +20204,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20241,12 +20253,12 @@
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -20316,7 +20328,7 @@
       </c>
       <c r="P161" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q161" s="2" t="inlineStr">
@@ -20365,7 +20377,7 @@
       </c>
       <c r="AC161" s="2" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AD161" s="2" t="inlineStr">
@@ -20440,7 +20452,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20489,12 +20501,132 @@
       </c>
       <c r="AC162" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
           <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr"/>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr"/>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr"/>
+      <c r="S163" s="2" t="inlineStr"/>
+      <c r="T163" s="2" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Z163" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA163" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB163" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC163" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AD163" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-operations.xlsx
+++ b/data/export/2026-09-18-operations.xlsx
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3209,12 +3209,12 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3577,12 +3577,12 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5428,12 +5428,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6420,12 +6420,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7913,12 +7913,12 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7988,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8112,7 +8112,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8285,12 +8285,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8776,12 +8776,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9402,7 +9402,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9645,7 +9645,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -10340,7 +10340,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD82" s="2" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11332,7 +11332,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
@@ -11429,24 +11429,24 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11505,12 +11505,12 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11553,24 +11553,24 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11672,27 +11672,31 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11700,7 +11704,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11724,12 +11728,12 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11749,12 +11753,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11792,29 +11796,29 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>66分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站唐陆公路龙东大道 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
@@ -11824,7 +11828,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11848,12 +11852,12 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11873,7 +11877,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
@@ -11916,27 +11920,31 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:21采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11944,7 +11952,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11968,17 +11976,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11988,12 +11996,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12036,29 +12044,29 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>21:23</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>20:21采样：该车到重点站博兴路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
@@ -12068,7 +12076,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12092,12 +12100,12 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -12117,12 +12125,12 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -12160,29 +12168,29 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:43</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -12192,7 +12200,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12216,12 +12224,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -12241,7 +12249,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12289,19 +12297,19 @@
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -12316,7 +12324,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12345,7 +12353,7 @@
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -12365,7 +12373,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12413,19 +12421,19 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数73分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站东陆路金海路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -12440,7 +12448,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12469,7 +12477,7 @@
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12484,12 +12492,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12564,7 +12572,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12608,17 +12616,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -12742,7 +12750,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -12866,7 +12874,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -12990,7 +12998,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13184,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13225,7 +13233,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
@@ -13354,7 +13362,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13486,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -13602,7 +13610,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13680,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13716,17 +13724,17 @@
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -13982,7 +13990,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -14052,7 +14060,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14101,12 +14109,12 @@
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -14308,7 +14316,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14357,12 +14365,12 @@
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -14432,7 +14440,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14481,12 +14489,12 @@
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14688,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14729,7 +14737,7 @@
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
@@ -14804,7 +14812,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14853,7 +14861,7 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
@@ -14982,7 +14990,7 @@
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -15052,7 +15060,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15101,7 +15109,7 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
@@ -15176,7 +15184,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15220,17 +15228,17 @@
       </c>
       <c r="AB119" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -15300,7 +15308,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15354,7 +15362,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -15478,7 +15486,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -15548,7 +15556,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15597,12 +15605,12 @@
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -15726,7 +15734,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -15792,7 +15800,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15970,7 +15978,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -16036,7 +16044,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16080,17 +16088,17 @@
       </c>
       <c r="AB126" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC126" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16218,7 @@
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -16334,7 +16342,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -16706,7 +16714,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16784,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16825,7 +16833,7 @@
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
@@ -16954,7 +16962,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -17078,7 +17086,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -17148,7 +17156,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17192,17 +17200,17 @@
       </c>
       <c r="AB135" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -17396,7 +17404,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17445,12 +17453,12 @@
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -17520,7 +17528,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17569,12 +17577,12 @@
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17652,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17693,12 +17701,12 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17776,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17817,7 +17825,7 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
@@ -18016,7 +18024,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18065,7 +18073,7 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
@@ -18190,7 +18198,7 @@
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -18260,7 +18268,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18314,7 +18322,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18392,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18433,7 +18441,7 @@
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
@@ -18508,7 +18516,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18686,7 +18694,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -18806,7 +18814,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18938,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -19054,7 +19062,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -19120,7 +19128,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19310,7 +19318,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -19558,7 +19566,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -19752,7 +19760,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19801,12 +19809,12 @@
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -19876,7 +19884,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19925,7 +19933,7 @@
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
@@ -20054,7 +20062,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -20178,7 +20186,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -20302,7 +20310,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20434,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -20550,7 +20558,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -20674,7 +20682,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -20798,7 +20806,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -20922,7 +20930,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -21124,7 +21132,7 @@
       </c>
       <c r="P167" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q167" s="2" t="inlineStr">
@@ -21168,17 +21176,17 @@
       </c>
       <c r="AB167" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC167" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -21248,7 +21256,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21292,17 +21300,17 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -21372,7 +21380,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21421,12 +21429,12 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -21496,7 +21504,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21545,12 +21553,12 @@
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21624,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21736,7 +21744,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21785,7 +21793,7 @@
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
@@ -21860,7 +21868,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21904,17 +21912,17 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -21984,7 +21992,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22038,7 +22046,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -22108,7 +22116,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22157,7 +22165,7 @@
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
@@ -22232,7 +22240,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22406,7 +22414,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22538,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -22650,7 +22658,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -22720,7 +22728,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22769,12 +22777,12 @@
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -23022,7 +23030,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -23270,7 +23278,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -23394,7 +23402,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -23432,12 +23440,12 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
@@ -23449,10 +23457,14 @@
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="N186" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -23460,7 +23472,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23484,12 +23496,12 @@
       </c>
       <c r="X186" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y186" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z186" s="2" t="inlineStr">
@@ -23509,7 +23521,7 @@
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
@@ -23557,12 +23569,12 @@
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr"/>
@@ -23584,7 +23596,7 @@
       </c>
       <c r="P187" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q187" s="2" t="inlineStr">
@@ -23633,7 +23645,7 @@
       </c>
       <c r="AC187" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AD187" s="2" t="inlineStr">
@@ -23681,26 +23693,22 @@
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
       <c r="M188" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站康沈路秀沿路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N188" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:40采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="N188" s="2" t="inlineStr"/>
       <c r="O188" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -23708,7 +23716,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23737,7 +23745,7 @@
       </c>
       <c r="Y188" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z188" s="2" t="inlineStr">
@@ -23757,12 +23765,12 @@
       </c>
       <c r="AC188" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -23805,19 +23813,19 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
       <c r="M189" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:31采样，终点ETA 26分钟</t>
         </is>
       </c>
       <c r="N189" s="2" t="inlineStr"/>
@@ -23828,7 +23836,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23852,17 +23860,17 @@
       </c>
       <c r="X189" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y189" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z189" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA189" s="2" t="inlineStr">
@@ -23872,17 +23880,17 @@
       </c>
       <c r="AB189" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -23920,27 +23928,31 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
       <c r="M190" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N190" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N190" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23948,7 +23960,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23972,17 +23984,17 @@
       </c>
       <c r="X190" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y190" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z190" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA190" s="2" t="inlineStr">
@@ -23992,17 +24004,17 @@
       </c>
       <c r="AB190" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -24035,12 +24047,12 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
@@ -24068,7 +24080,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24076,10 +24088,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R191" s="2" t="inlineStr"/>
-      <c r="S191" s="2" t="inlineStr"/>
-      <c r="T191" s="2" t="inlineStr"/>
-      <c r="U191" s="2" t="inlineStr"/>
+      <c r="R191" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="S191" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="T191" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="U191" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V191" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24097,7 +24125,7 @@
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
@@ -24122,7 +24150,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -24160,29 +24188,29 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O192" s="2" t="inlineStr">
@@ -24192,7 +24220,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24216,12 +24244,12 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
@@ -24241,12 +24269,12 @@
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -24284,29 +24312,29 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>21:27</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O193" s="2" t="inlineStr">
@@ -24316,7 +24344,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24340,12 +24368,12 @@
       </c>
       <c r="X193" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y193" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z193" s="2" t="inlineStr">
@@ -24365,12 +24393,12 @@
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -24403,12 +24431,12 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -24436,7 +24464,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24444,10 +24472,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R194" s="2" t="inlineStr"/>
-      <c r="S194" s="2" t="inlineStr"/>
-      <c r="T194" s="2" t="inlineStr"/>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="R194" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S194" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="V194" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24465,7 +24509,7 @@
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
@@ -24538,21 +24582,17 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr"/>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -24560,7 +24600,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24584,12 +24624,12 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
@@ -24609,7 +24649,7 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
@@ -24657,19 +24697,19 @@
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr"/>
@@ -24680,7 +24720,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24704,17 +24744,17 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA196" s="2" t="inlineStr">
@@ -24724,17 +24764,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -24777,24 +24817,24 @@
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±7分钟</t>
+          <t>21:21采样：该车到重点站沪南路御桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O197" s="2" t="inlineStr">
@@ -24804,7 +24844,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24853,7 +24893,7 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
@@ -24906,14 +24946,14 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数113分钟，约±5分钟</t>
+          <t>21:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
@@ -24928,7 +24968,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24977,7 +25017,7 @@
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
@@ -25025,19 +25065,19 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±7分钟</t>
+          <t>21:21采样：该车到重点站锦绣路花木路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
@@ -25052,7 +25092,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25081,7 +25121,7 @@
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
@@ -25101,12 +25141,12 @@
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -25154,14 +25194,14 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -25176,7 +25216,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25205,7 +25245,7 @@
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
@@ -25225,7 +25265,7 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
@@ -25296,7 +25336,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25345,7 +25385,7 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
@@ -25784,7 +25824,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25908,7 +25948,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25957,12 +25997,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26082,7 +26122,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -26272,7 +26312,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26321,7 +26361,7 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26396,7 +26436,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26445,12 +26485,12 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26614,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26698,7 +26738,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -26942,7 +26982,7 @@
       </c>
       <c r="AD214" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -27136,7 +27176,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27185,12 +27225,12 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27300,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27309,7 +27349,7 @@
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
@@ -27880,7 +27920,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -28248,7 +28288,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28297,12 +28337,12 @@
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28426,7 +28466,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28496,7 +28536,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28545,12 +28585,12 @@
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -28620,7 +28660,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28669,7 +28709,7 @@
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
@@ -28798,7 +28838,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -28922,7 +28962,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -29240,7 +29280,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29289,12 +29329,12 @@
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29648,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29988,7 +30028,7 @@
       </c>
       <c r="P239" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q239" s="2" t="inlineStr">
@@ -30049,12 +30089,12 @@
       </c>
       <c r="AC239" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -30178,7 +30218,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -30302,7 +30342,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -30426,7 +30466,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -31290,7 +31330,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -31414,7 +31454,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -31538,7 +31578,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32352,7 +32392,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32401,7 +32441,7 @@
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
@@ -32526,7 +32566,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32650,7 +32690,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -32770,7 +32810,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32894,7 +32934,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -32960,7 +33000,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33009,12 +33049,12 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33084,7 +33124,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33133,7 +33173,7 @@
       </c>
       <c r="AC264" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD264" s="2" t="inlineStr">
@@ -33576,7 +33616,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33700,7 +33740,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33749,12 +33789,12 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -34068,7 +34108,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34117,12 +34157,12 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34440,7 +34480,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34489,7 +34529,7 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34614,7 +34654,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34734,7 +34774,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -34858,7 +34898,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34982,7 +35022,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -35176,7 +35216,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35225,12 +35265,12 @@
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35300,7 +35340,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35349,7 +35389,7 @@
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
@@ -35672,7 +35712,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35796,7 +35836,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35845,12 +35885,12 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -36168,7 +36208,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36217,12 +36257,12 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36590,7 +36630,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36656,7 +36696,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36705,7 +36745,7 @@
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
@@ -36834,7 +36874,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -36958,7 +36998,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -37152,7 +37192,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37201,12 +37241,12 @@
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37276,7 +37316,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37385,12 +37425,12 @@
       <c r="L299" s="2" t="inlineStr"/>
       <c r="M299" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N299" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O299" s="2" t="inlineStr">
@@ -37400,7 +37440,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37449,7 +37489,7 @@
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
@@ -37492,29 +37532,29 @@
       </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站五莲路凌河路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N300" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O300" s="2" t="inlineStr">
@@ -37524,7 +37564,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37548,12 +37588,12 @@
       </c>
       <c r="X300" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y300" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z300" s="2" t="inlineStr">
@@ -37573,12 +37613,12 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -37616,24 +37656,24 @@
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站杨高北路航津路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数57分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr">
@@ -37648,7 +37688,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37672,12 +37712,12 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
@@ -37697,12 +37737,12 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -37740,29 +37780,29 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站云山路灵山路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37772,7 +37812,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37796,12 +37836,12 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
@@ -37821,7 +37861,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37869,26 +37909,22 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>21:56</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数76分钟估算，约±8分钟</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 43分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr"/>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37896,7 +37932,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37920,12 +37956,12 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
@@ -37945,12 +37981,12 @@
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37993,24 +38029,24 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±10分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±11分钟</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O304" s="2" t="inlineStr">
@@ -38020,7 +38056,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38044,12 +38080,12 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
@@ -38069,7 +38105,7 @@
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.2</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
@@ -38144,7 +38180,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38193,12 +38229,12 @@
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-operations.xlsx
+++ b/data/export/2026-09-18-operations.xlsx
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6425,7 +6425,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8657,7 +8657,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8781,7 +8781,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
@@ -11332,7 +11332,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11629,7 +11629,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -12001,7 +12001,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12292,29 +12292,29 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站唐陆公路春雅路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12416,29 +12416,29 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站东陆路金海路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12472,12 +12472,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12497,7 +12497,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12874,7 +12874,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="P110" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q110" s="2" t="inlineStr">
@@ -14109,7 +14109,7 @@
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AD110" s="2" t="inlineStr">
@@ -14316,7 +14316,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14360,17 +14360,17 @@
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14688,7 @@
       </c>
       <c r="P115" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q115" s="2" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="AC115" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AD115" s="2" t="inlineStr">
@@ -14812,7 +14812,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14861,7 +14861,7 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16342,7 +16342,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
       </c>
       <c r="P132" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q132" s="2" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="AC132" s="2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AD132" s="2" t="inlineStr">
@@ -17404,7 +17404,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17453,7 +17453,7 @@
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
@@ -17528,7 +17528,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17572,17 +17572,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
@@ -18024,7 +18024,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="AC142" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD142" s="2" t="inlineStr">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18814,7 +18814,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -21504,7 +21504,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21553,7 +21553,7 @@
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
@@ -21744,7 +21744,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21793,7 +21793,7 @@
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
@@ -21868,7 +21868,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -22116,7 +22116,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
@@ -22240,7 +22240,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -22728,7 +22728,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22772,17 +22772,17 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -23472,7 +23472,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23521,7 +23521,7 @@
       </c>
       <c r="AC186" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD186" s="2" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -24317,24 +24317,24 @@
       </c>
       <c r="I193" s="2" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
       <c r="M193" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N193" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O193" s="2" t="inlineStr">
@@ -24344,7 +24344,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="AC193" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AD193" s="2" t="inlineStr">
@@ -24436,7 +24436,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -24464,7 +24464,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24572,27 +24572,31 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -24600,7 +24604,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24624,12 +24628,12 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
@@ -24649,7 +24653,7 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
@@ -24692,7 +24696,7 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -24709,10 +24713,14 @@
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24720,7 +24728,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24744,12 +24752,12 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
@@ -24812,29 +24820,29 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站沪南路御桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N197" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O197" s="2" t="inlineStr">
@@ -24844,7 +24852,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24868,12 +24876,12 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
@@ -24893,7 +24901,7 @@
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
@@ -24941,26 +24949,22 @@
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr"/>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -24968,7 +24972,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -24992,12 +24996,12 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
@@ -25017,7 +25021,7 @@
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
@@ -25065,26 +25069,22 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站锦绣路花木路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 47分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr"/>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -25092,7 +25092,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25116,17 +25116,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -25136,17 +25136,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -25189,19 +25189,19 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
+          <t>21:50采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -25216,7 +25216,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25265,7 +25265,7 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
@@ -25336,7 +25336,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25385,7 +25385,7 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
@@ -25948,7 +25948,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25997,12 +25997,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -26122,7 +26122,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -26312,7 +26312,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -27176,7 +27176,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27225,7 +27225,7 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -27300,7 +27300,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27349,7 +27349,7 @@
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
@@ -28288,7 +28288,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28337,12 +28337,12 @@
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -28466,7 +28466,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -28660,7 +28660,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28838,7 +28838,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28962,7 +28962,7 @@
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29329,7 +29329,7 @@
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -30342,7 +30342,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -30466,7 +30466,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -31330,7 +31330,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -31454,7 +31454,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -31578,7 +31578,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32392,7 +32392,7 @@
       </c>
       <c r="P258" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q258" s="2" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="AC258" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AD258" s="2" t="inlineStr">
@@ -32566,7 +32566,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -32690,7 +32690,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -32810,7 +32810,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -33000,7 +33000,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33049,12 +33049,12 @@
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -33124,7 +33124,7 @@
       </c>
       <c r="P264" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q264" s="2" t="inlineStr">
@@ -33740,7 +33740,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33789,7 +33789,7 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
@@ -34480,7 +34480,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34529,7 +34529,7 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
@@ -34654,7 +34654,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -34774,7 +34774,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34898,7 +34898,7 @@
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -35216,7 +35216,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35265,12 +35265,12 @@
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -35340,7 +35340,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35836,7 +35836,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35885,7 +35885,7 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -36630,7 +36630,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36696,7 +36696,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36745,7 +36745,7 @@
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
@@ -36998,7 +36998,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -37192,7 +37192,7 @@
       </c>
       <c r="P297" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q297" s="2" t="inlineStr">
@@ -37241,12 +37241,12 @@
       </c>
       <c r="AC297" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37440,7 +37440,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37737,7 +37737,7 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
@@ -37785,24 +37785,24 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37812,7 +37812,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37861,7 +37861,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.2</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37904,27 +37904,31 @@
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>21:55</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 43分钟</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37932,7 +37936,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37956,12 +37960,12 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
@@ -37981,12 +37985,12 @@
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -38024,12 +38028,12 @@
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
@@ -38041,12 +38045,12 @@
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O304" s="2" t="inlineStr">
@@ -38056,7 +38060,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38080,12 +38084,12 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
@@ -38153,19 +38157,19 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数81分钟估算，约±5分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N305" s="2" t="inlineStr">
@@ -38180,7 +38184,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38209,7 +38213,7 @@
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
@@ -38229,7 +38233,7 @@
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">

--- a/data/export/2026-09-18-operations.xlsx
+++ b/data/export/2026-09-18-operations.xlsx
@@ -454,7 +454,7 @@
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="20" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
     <col width="18" customWidth="1" min="28" max="28"/>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14360,17 +14360,17 @@
       </c>
       <c r="AB112" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC112" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -14812,7 +14812,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -16342,7 +16342,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17572,17 +17572,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="P142" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="Q142" s="2" t="inlineStr">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -18814,7 +18814,7 @@
       </c>
       <c r="AD148" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -19938,7 +19938,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -22728,7 +22728,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22772,17 +22772,17 @@
       </c>
       <c r="AB180" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -23472,7 +23472,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -25064,27 +25064,31 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -25092,7 +25096,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25116,17 +25120,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -25136,17 +25140,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -25201,14 +25205,10 @@
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>21:50采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：22:29采样，终点ETA 23分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr"/>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -25216,7 +25216,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25240,12 +25240,12 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
@@ -27176,7 +27176,7 @@
       </c>
       <c r="P216" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q216" s="2" t="inlineStr">
@@ -27225,7 +27225,7 @@
       </c>
       <c r="AC216" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD216" s="2" t="inlineStr">
@@ -29280,7 +29280,7 @@
       </c>
       <c r="P233" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q233" s="2" t="inlineStr">
@@ -29329,7 +29329,7 @@
       </c>
       <c r="AC233" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD233" s="2" t="inlineStr">
@@ -33740,7 +33740,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33789,7 +33789,7 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
@@ -35836,7 +35836,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35885,7 +35885,7 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
@@ -37688,7 +37688,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37737,7 +37737,7 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
@@ -38157,26 +38157,22 @@
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>21:50采样：该车到重点站金杨路云山路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：22:28采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr"/>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -38184,7 +38180,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38208,12 +38204,12 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
@@ -38233,7 +38229,7 @@
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
